--- a/price.xlsx
+++ b/price.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vencedor\IdeaProjects\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView showSheetTabs="0" xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="0"/>
+    <workbookView showSheetTabs="0" xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.00&quot; грн.&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; грн.&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;₴&quot;"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -145,7 +144,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -162,10 +161,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -602,15 +598,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IT6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="1" customWidth="1"/>
-    <col min="4" max="254" width="10.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="1" customWidth="1"/>
+    <col min="4" max="254" width="10.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -621,7 +617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>123</v>
       </c>
@@ -632,7 +628,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>568</v>
       </c>
@@ -643,7 +639,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>890</v>
       </c>
@@ -654,18 +650,18 @@
         <v>734</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1432</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>2398</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>2345</v>
       </c>
@@ -679,7 +675,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.74791666666666667" right="0.74791666666666667" top="0.98402777777777772" bottom="0.98402777777777772" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>